--- a/NT_AirPollution.Web/App_Data/Payment/Template/結清證明.xlsx
+++ b/NT_AirPollution.Web/App_Data/Payment/Template/結清證明.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\case\Alvin\NT_AirPollution\NT_AirPollution.Web\App_Data\Payment\Template\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\owner\Desktop\暫時\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88C0C873-4879-47B7-8900-B533D653B24A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC284FAF-C3BB-40FF-870F-5053B8166467}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="14160" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="結清證明" sheetId="60" r:id="rId1"/>
@@ -21,18 +21,6 @@
     <definedName name="www">#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -150,7 +138,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12">
+  <fonts count="11">
     <font>
       <sz val="12"/>
       <name val="新細明體"/>
@@ -206,14 +194,6 @@
       <charset val="136"/>
     </font>
     <font>
-      <sz val="14"/>
-      <name val="標楷體"/>
-      <family val="4"/>
-      <charset val="136"/>
-    </font>
-    <font>
-      <b/>
-      <u/>
       <sz val="14"/>
       <name val="標楷體"/>
       <family val="4"/>
@@ -326,7 +306,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -355,27 +335,18 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -391,62 +362,68 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -822,139 +799,139 @@
     <col min="2" max="18" width="4.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="40.5" customHeight="1">
-      <c r="A1" s="42" t="s">
+    <row r="1" spans="1:20" ht="34.35" customHeight="1">
+      <c r="A1" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="E1" s="42"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="42"/>
-      <c r="I1" s="42"/>
-      <c r="J1" s="42"/>
-      <c r="K1" s="42"/>
-      <c r="L1" s="42"/>
-      <c r="M1" s="42"/>
-      <c r="N1" s="42"/>
-      <c r="O1" s="42"/>
-      <c r="P1" s="42"/>
-      <c r="Q1" s="42"/>
-      <c r="R1" s="42"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="26"/>
+      <c r="K1" s="26"/>
+      <c r="L1" s="26"/>
+      <c r="M1" s="26"/>
+      <c r="N1" s="26"/>
+      <c r="O1" s="26"/>
+      <c r="P1" s="26"/>
+      <c r="Q1" s="26"/>
+      <c r="R1" s="26"/>
       <c r="S1" s="10"/>
     </row>
-    <row r="2" spans="1:20" s="10" customFormat="1" ht="30" customHeight="1">
-      <c r="A2" s="12" t="s">
+    <row r="2" spans="1:20" s="10" customFormat="1" ht="34.35" customHeight="1">
+      <c r="A2" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="43"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
-      <c r="F2" s="43"/>
-      <c r="G2" s="43"/>
-      <c r="H2" s="43"/>
-      <c r="I2" s="43"/>
-      <c r="J2" s="43"/>
-      <c r="K2" s="43"/>
-      <c r="L2" s="43"/>
-      <c r="M2" s="43"/>
-      <c r="N2" s="43"/>
-      <c r="O2" s="43"/>
-      <c r="P2" s="43"/>
-      <c r="Q2" s="43"/>
-      <c r="R2" s="44"/>
+      <c r="B2" s="37"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
+      <c r="J2" s="38"/>
+      <c r="K2" s="38"/>
+      <c r="L2" s="38"/>
+      <c r="M2" s="38"/>
+      <c r="N2" s="38"/>
+      <c r="O2" s="38"/>
+      <c r="P2" s="38"/>
+      <c r="Q2" s="38"/>
+      <c r="R2" s="39"/>
       <c r="S2" s="9"/>
     </row>
-    <row r="3" spans="1:20" s="9" customFormat="1" ht="30" customHeight="1">
-      <c r="A3" s="13" t="s">
+    <row r="3" spans="1:20" s="9" customFormat="1" ht="34.35" customHeight="1">
+      <c r="A3" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="45"/>
-      <c r="C3" s="45"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="45"/>
-      <c r="G3" s="45"/>
-      <c r="H3" s="45"/>
-      <c r="I3" s="45"/>
-      <c r="J3" s="45"/>
-      <c r="K3" s="45"/>
-      <c r="L3" s="45"/>
-      <c r="M3" s="45"/>
-      <c r="N3" s="45"/>
-      <c r="O3" s="45"/>
-      <c r="P3" s="45"/>
-      <c r="Q3" s="45"/>
-      <c r="R3" s="46"/>
-    </row>
-    <row r="4" spans="1:20" s="9" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A4" s="31" t="s">
+      <c r="B3" s="41"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="42"/>
+      <c r="H3" s="42"/>
+      <c r="I3" s="42"/>
+      <c r="J3" s="42"/>
+      <c r="K3" s="42"/>
+      <c r="L3" s="42"/>
+      <c r="M3" s="42"/>
+      <c r="N3" s="42"/>
+      <c r="O3" s="42"/>
+      <c r="P3" s="42"/>
+      <c r="Q3" s="42"/>
+      <c r="R3" s="43"/>
+    </row>
+    <row r="4" spans="1:20" s="9" customFormat="1" ht="34.35" customHeight="1">
+      <c r="A4" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="32"/>
-      <c r="C4" s="33"/>
-      <c r="D4" s="33"/>
-      <c r="E4" s="33"/>
-      <c r="F4" s="33"/>
-      <c r="G4" s="33"/>
-      <c r="H4" s="33"/>
-      <c r="I4" s="33"/>
-      <c r="J4" s="33"/>
-      <c r="K4" s="33"/>
-      <c r="L4" s="33"/>
-      <c r="M4" s="33"/>
-      <c r="N4" s="33"/>
-      <c r="O4" s="33"/>
-      <c r="P4" s="33"/>
-      <c r="Q4" s="33"/>
-      <c r="R4" s="34"/>
-    </row>
-    <row r="5" spans="1:20" s="9" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A5" s="31" t="s">
+      <c r="B4" s="44"/>
+      <c r="C4" s="44"/>
+      <c r="D4" s="44"/>
+      <c r="E4" s="44"/>
+      <c r="F4" s="44"/>
+      <c r="G4" s="44"/>
+      <c r="H4" s="44"/>
+      <c r="I4" s="44"/>
+      <c r="J4" s="44"/>
+      <c r="K4" s="44"/>
+      <c r="L4" s="44"/>
+      <c r="M4" s="44"/>
+      <c r="N4" s="44"/>
+      <c r="O4" s="44"/>
+      <c r="P4" s="44"/>
+      <c r="Q4" s="44"/>
+      <c r="R4" s="45"/>
+    </row>
+    <row r="5" spans="1:20" s="9" customFormat="1" ht="34.35" customHeight="1">
+      <c r="A5" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="32"/>
-      <c r="C5" s="33"/>
-      <c r="D5" s="33"/>
-      <c r="E5" s="33"/>
-      <c r="F5" s="33"/>
-      <c r="G5" s="33"/>
-      <c r="H5" s="33"/>
-      <c r="I5" s="33"/>
-      <c r="J5" s="33"/>
-      <c r="K5" s="33"/>
-      <c r="L5" s="33"/>
-      <c r="M5" s="33"/>
-      <c r="N5" s="33"/>
-      <c r="O5" s="33"/>
-      <c r="P5" s="33"/>
-      <c r="Q5" s="33"/>
-      <c r="R5" s="34"/>
-    </row>
-    <row r="6" spans="1:20" s="9" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A6" s="31" t="s">
+      <c r="B5" s="44"/>
+      <c r="C5" s="44"/>
+      <c r="D5" s="44"/>
+      <c r="E5" s="44"/>
+      <c r="F5" s="44"/>
+      <c r="G5" s="44"/>
+      <c r="H5" s="44"/>
+      <c r="I5" s="44"/>
+      <c r="J5" s="44"/>
+      <c r="K5" s="44"/>
+      <c r="L5" s="44"/>
+      <c r="M5" s="44"/>
+      <c r="N5" s="44"/>
+      <c r="O5" s="44"/>
+      <c r="P5" s="44"/>
+      <c r="Q5" s="44"/>
+      <c r="R5" s="45"/>
+    </row>
+    <row r="6" spans="1:20" s="9" customFormat="1" ht="34.35" customHeight="1">
+      <c r="A6" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="32"/>
-      <c r="C6" s="35"/>
-      <c r="D6" s="35"/>
-      <c r="E6" s="35"/>
-      <c r="F6" s="35"/>
-      <c r="G6" s="35"/>
-      <c r="H6" s="35"/>
-      <c r="I6" s="35"/>
-      <c r="J6" s="35"/>
-      <c r="K6" s="35"/>
-      <c r="L6" s="35"/>
-      <c r="M6" s="35"/>
-      <c r="N6" s="35"/>
-      <c r="O6" s="35"/>
-      <c r="P6" s="35"/>
-      <c r="Q6" s="35"/>
-      <c r="R6" s="36"/>
+      <c r="B6" s="44"/>
+      <c r="C6" s="44"/>
+      <c r="D6" s="44"/>
+      <c r="E6" s="44"/>
+      <c r="F6" s="44"/>
+      <c r="G6" s="44"/>
+      <c r="H6" s="44"/>
+      <c r="I6" s="44"/>
+      <c r="J6" s="44"/>
+      <c r="K6" s="44"/>
+      <c r="L6" s="44"/>
+      <c r="M6" s="44"/>
+      <c r="N6" s="44"/>
+      <c r="O6" s="44"/>
+      <c r="P6" s="44"/>
+      <c r="Q6" s="44"/>
+      <c r="R6" s="45"/>
     </row>
     <row r="7" spans="1:20" ht="35.1" customHeight="1">
       <c r="A7" s="4"/>
@@ -977,248 +954,248 @@
       <c r="R7" s="3"/>
     </row>
     <row r="8" spans="1:20" ht="35.1" customHeight="1">
-      <c r="A8" s="37" t="s">
+      <c r="A8" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="38"/>
-      <c r="C8" s="38"/>
-      <c r="D8" s="38"/>
-      <c r="E8" s="38"/>
-      <c r="F8" s="38"/>
-      <c r="G8" s="38"/>
-      <c r="H8" s="38"/>
-      <c r="I8" s="38"/>
-      <c r="J8" s="38"/>
-      <c r="K8" s="38"/>
-      <c r="L8" s="38"/>
-      <c r="M8" s="38"/>
-      <c r="N8" s="38"/>
-      <c r="O8" s="38"/>
-      <c r="P8" s="38"/>
-      <c r="Q8" s="38"/>
-      <c r="R8" s="39"/>
+      <c r="B8" s="32"/>
+      <c r="C8" s="32"/>
+      <c r="D8" s="32"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="32"/>
+      <c r="G8" s="32"/>
+      <c r="H8" s="32"/>
+      <c r="I8" s="32"/>
+      <c r="J8" s="32"/>
+      <c r="K8" s="32"/>
+      <c r="L8" s="32"/>
+      <c r="M8" s="32"/>
+      <c r="N8" s="32"/>
+      <c r="O8" s="32"/>
+      <c r="P8" s="32"/>
+      <c r="Q8" s="32"/>
+      <c r="R8" s="33"/>
     </row>
     <row r="9" spans="1:20" s="8" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A9" s="15" t="s">
+      <c r="A9" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="7">
-        <v>0</v>
-      </c>
-      <c r="C9" s="16" t="s">
+      <c r="B9" s="13">
+        <v>0</v>
+      </c>
+      <c r="C9" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="7">
-        <v>0</v>
-      </c>
-      <c r="E9" s="16" t="s">
+      <c r="D9" s="13">
+        <v>0</v>
+      </c>
+      <c r="E9" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="7">
-        <v>0</v>
-      </c>
-      <c r="G9" s="16" t="s">
+      <c r="F9" s="13">
+        <v>0</v>
+      </c>
+      <c r="G9" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="H9" s="7">
-        <v>0</v>
-      </c>
-      <c r="I9" s="16" t="s">
+      <c r="H9" s="13">
+        <v>0</v>
+      </c>
+      <c r="I9" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="J9" s="7">
-        <v>0</v>
-      </c>
-      <c r="K9" s="16" t="s">
+      <c r="J9" s="13">
+        <v>0</v>
+      </c>
+      <c r="K9" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="L9" s="7">
-        <v>0</v>
-      </c>
-      <c r="M9" s="16" t="s">
+      <c r="L9" s="13">
+        <v>0</v>
+      </c>
+      <c r="M9" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="N9" s="7">
-        <v>0</v>
-      </c>
-      <c r="O9" s="16" t="s">
+      <c r="N9" s="13">
+        <v>0</v>
+      </c>
+      <c r="O9" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="P9" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="16" t="s">
+      <c r="P9" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="R9" s="17" t="s">
+      <c r="R9" s="14" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:20" s="8" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A10" s="15" t="s">
+      <c r="A10" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="7">
-        <v>0</v>
-      </c>
-      <c r="C10" s="16" t="s">
+      <c r="B10" s="13">
+        <v>0</v>
+      </c>
+      <c r="C10" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="7">
-        <v>0</v>
-      </c>
-      <c r="E10" s="16" t="s">
+      <c r="D10" s="13">
+        <v>0</v>
+      </c>
+      <c r="E10" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="F10" s="7">
-        <v>0</v>
-      </c>
-      <c r="G10" s="16" t="s">
+      <c r="F10" s="13">
+        <v>0</v>
+      </c>
+      <c r="G10" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="H10" s="7">
-        <v>0</v>
-      </c>
-      <c r="I10" s="16" t="s">
+      <c r="H10" s="13">
+        <v>0</v>
+      </c>
+      <c r="I10" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="J10" s="7">
-        <v>0</v>
-      </c>
-      <c r="K10" s="16" t="s">
+      <c r="J10" s="13">
+        <v>0</v>
+      </c>
+      <c r="K10" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="L10" s="7">
-        <v>0</v>
-      </c>
-      <c r="M10" s="16" t="s">
+      <c r="L10" s="13">
+        <v>0</v>
+      </c>
+      <c r="M10" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="N10" s="7">
-        <v>0</v>
-      </c>
-      <c r="O10" s="16" t="s">
+      <c r="N10" s="13">
+        <v>0</v>
+      </c>
+      <c r="O10" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="P10" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="16" t="s">
+      <c r="P10" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="R10" s="17" t="s">
+      <c r="R10" s="14" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:20" s="8" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A11" s="15" t="s">
+      <c r="A11" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="7">
-        <v>0</v>
-      </c>
-      <c r="C11" s="16" t="s">
+      <c r="B11" s="13">
+        <v>0</v>
+      </c>
+      <c r="C11" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="7">
-        <v>0</v>
-      </c>
-      <c r="E11" s="16" t="s">
+      <c r="D11" s="13">
+        <v>0</v>
+      </c>
+      <c r="E11" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="F11" s="7">
-        <v>0</v>
-      </c>
-      <c r="G11" s="16" t="s">
+      <c r="F11" s="13">
+        <v>0</v>
+      </c>
+      <c r="G11" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="H11" s="7">
-        <v>0</v>
-      </c>
-      <c r="I11" s="16" t="s">
+      <c r="H11" s="13">
+        <v>0</v>
+      </c>
+      <c r="I11" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="J11" s="7">
-        <v>0</v>
-      </c>
-      <c r="K11" s="16" t="s">
+      <c r="J11" s="13">
+        <v>0</v>
+      </c>
+      <c r="K11" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="L11" s="7">
-        <v>0</v>
-      </c>
-      <c r="M11" s="16" t="s">
+      <c r="L11" s="13">
+        <v>0</v>
+      </c>
+      <c r="M11" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="N11" s="7">
-        <v>0</v>
-      </c>
-      <c r="O11" s="16" t="s">
+      <c r="N11" s="13">
+        <v>0</v>
+      </c>
+      <c r="O11" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="P11" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="16" t="s">
+      <c r="P11" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="R11" s="17" t="s">
+      <c r="R11" s="14" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:20" s="8" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A12" s="15" t="s">
+      <c r="A12" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="7">
-        <v>0</v>
-      </c>
-      <c r="C12" s="16" t="s">
+      <c r="B12" s="13">
+        <v>0</v>
+      </c>
+      <c r="C12" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="7">
-        <v>0</v>
-      </c>
-      <c r="E12" s="16" t="s">
+      <c r="D12" s="13">
+        <v>0</v>
+      </c>
+      <c r="E12" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="F12" s="7">
-        <v>0</v>
-      </c>
-      <c r="G12" s="16" t="s">
+      <c r="F12" s="13">
+        <v>0</v>
+      </c>
+      <c r="G12" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="H12" s="7">
-        <v>0</v>
-      </c>
-      <c r="I12" s="16" t="s">
+      <c r="H12" s="13">
+        <v>0</v>
+      </c>
+      <c r="I12" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="J12" s="7">
-        <v>0</v>
-      </c>
-      <c r="K12" s="16" t="s">
+      <c r="J12" s="13">
+        <v>0</v>
+      </c>
+      <c r="K12" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="L12" s="7">
-        <v>0</v>
-      </c>
-      <c r="M12" s="16" t="s">
+      <c r="L12" s="13">
+        <v>0</v>
+      </c>
+      <c r="M12" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="N12" s="7">
-        <v>0</v>
-      </c>
-      <c r="O12" s="16" t="s">
+      <c r="N12" s="13">
+        <v>0</v>
+      </c>
+      <c r="O12" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="P12" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="16" t="s">
+      <c r="P12" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="R12" s="17" t="s">
+      <c r="R12" s="14" t="s">
         <v>12</v>
       </c>
       <c r="T12" s="11" t="s">
@@ -1226,304 +1203,304 @@
       </c>
     </row>
     <row r="13" spans="1:20" s="8" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A13" s="37"/>
-      <c r="B13" s="38"/>
-      <c r="C13" s="38"/>
-      <c r="D13" s="38"/>
-      <c r="E13" s="38"/>
-      <c r="F13" s="38"/>
-      <c r="G13" s="38"/>
-      <c r="H13" s="38"/>
-      <c r="I13" s="38"/>
-      <c r="J13" s="38"/>
-      <c r="K13" s="38"/>
-      <c r="L13" s="38"/>
-      <c r="M13" s="38"/>
-      <c r="N13" s="38"/>
-      <c r="O13" s="38"/>
-      <c r="P13" s="38"/>
-      <c r="Q13" s="38"/>
-      <c r="R13" s="39"/>
+      <c r="A13" s="31"/>
+      <c r="B13" s="32"/>
+      <c r="C13" s="32"/>
+      <c r="D13" s="32"/>
+      <c r="E13" s="32"/>
+      <c r="F13" s="32"/>
+      <c r="G13" s="32"/>
+      <c r="H13" s="32"/>
+      <c r="I13" s="32"/>
+      <c r="J13" s="32"/>
+      <c r="K13" s="32"/>
+      <c r="L13" s="32"/>
+      <c r="M13" s="32"/>
+      <c r="N13" s="32"/>
+      <c r="O13" s="32"/>
+      <c r="P13" s="32"/>
+      <c r="Q13" s="32"/>
+      <c r="R13" s="33"/>
     </row>
     <row r="14" spans="1:20" s="8" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A14" s="14"/>
-      <c r="B14" s="7">
-        <v>0</v>
-      </c>
-      <c r="C14" s="16" t="s">
+      <c r="A14" s="35"/>
+      <c r="B14" s="13">
+        <v>0</v>
+      </c>
+      <c r="C14" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="D14" s="7">
-        <v>0</v>
-      </c>
-      <c r="E14" s="16" t="s">
+      <c r="D14" s="13">
+        <v>0</v>
+      </c>
+      <c r="E14" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="F14" s="7">
-        <v>0</v>
-      </c>
-      <c r="G14" s="16" t="s">
+      <c r="F14" s="13">
+        <v>0</v>
+      </c>
+      <c r="G14" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="H14" s="7">
-        <v>0</v>
-      </c>
-      <c r="I14" s="16" t="s">
+      <c r="H14" s="13">
+        <v>0</v>
+      </c>
+      <c r="I14" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="J14" s="7">
-        <v>0</v>
-      </c>
-      <c r="K14" s="16" t="s">
+      <c r="J14" s="13">
+        <v>0</v>
+      </c>
+      <c r="K14" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="7">
-        <v>0</v>
-      </c>
-      <c r="M14" s="16" t="s">
+      <c r="L14" s="13">
+        <v>0</v>
+      </c>
+      <c r="M14" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="N14" s="7">
-        <v>0</v>
-      </c>
-      <c r="O14" s="16" t="s">
+      <c r="N14" s="13">
+        <v>0</v>
+      </c>
+      <c r="O14" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="P14" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="16" t="s">
+      <c r="P14" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="R14" s="17" t="s">
+      <c r="R14" s="14" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:20" s="8" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A15" s="14"/>
+      <c r="A15" s="12"/>
       <c r="B15" s="7"/>
-      <c r="C15" s="16"/>
+      <c r="C15" s="13"/>
       <c r="D15" s="7"/>
-      <c r="E15" s="16"/>
+      <c r="E15" s="13"/>
       <c r="F15" s="7"/>
-      <c r="G15" s="16"/>
+      <c r="G15" s="13"/>
       <c r="H15" s="7"/>
-      <c r="I15" s="16"/>
+      <c r="I15" s="13"/>
       <c r="J15" s="7"/>
-      <c r="K15" s="16"/>
+      <c r="K15" s="13"/>
       <c r="L15" s="7"/>
-      <c r="M15" s="16"/>
+      <c r="M15" s="13"/>
       <c r="N15" s="7"/>
-      <c r="O15" s="16"/>
+      <c r="O15" s="13"/>
       <c r="P15" s="7"/>
-      <c r="Q15" s="16"/>
-      <c r="R15" s="17"/>
+      <c r="Q15" s="13"/>
+      <c r="R15" s="14"/>
     </row>
     <row r="16" spans="1:20" ht="16.149999999999999" customHeight="1">
-      <c r="A16" s="18"/>
-      <c r="B16" s="19"/>
-      <c r="C16" s="19"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="19"/>
-      <c r="G16" s="19"/>
-      <c r="H16" s="19"/>
-      <c r="I16" s="19"/>
-      <c r="J16" s="19"/>
-      <c r="K16" s="19"/>
-      <c r="L16" s="19"/>
-      <c r="M16" s="19"/>
-      <c r="N16" s="19"/>
-      <c r="O16" s="19"/>
-      <c r="P16" s="19"/>
-      <c r="Q16" s="19"/>
-      <c r="R16" s="20"/>
+      <c r="A16" s="15"/>
+      <c r="B16" s="16"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="16"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="16"/>
+      <c r="H16" s="16"/>
+      <c r="I16" s="16"/>
+      <c r="J16" s="16"/>
+      <c r="K16" s="16"/>
+      <c r="L16" s="16"/>
+      <c r="M16" s="16"/>
+      <c r="N16" s="16"/>
+      <c r="O16" s="16"/>
+      <c r="P16" s="16"/>
+      <c r="Q16" s="16"/>
+      <c r="R16" s="17"/>
     </row>
     <row r="17" spans="1:20">
-      <c r="A17" s="18"/>
-      <c r="B17" s="19"/>
-      <c r="C17" s="19"/>
-      <c r="D17" s="19"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="19"/>
-      <c r="G17" s="19"/>
-      <c r="H17" s="19"/>
-      <c r="I17" s="19"/>
-      <c r="J17" s="19"/>
-      <c r="K17" s="19"/>
-      <c r="L17" s="19"/>
-      <c r="M17" s="19"/>
-      <c r="N17" s="19"/>
-      <c r="O17" s="19"/>
-      <c r="P17" s="19"/>
-      <c r="Q17" s="19"/>
-      <c r="R17" s="20"/>
+      <c r="A17" s="15"/>
+      <c r="B17" s="16"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="16"/>
+      <c r="H17" s="16"/>
+      <c r="I17" s="16"/>
+      <c r="J17" s="16"/>
+      <c r="K17" s="16"/>
+      <c r="L17" s="16"/>
+      <c r="M17" s="16"/>
+      <c r="N17" s="16"/>
+      <c r="O17" s="16"/>
+      <c r="P17" s="16"/>
+      <c r="Q17" s="16"/>
+      <c r="R17" s="17"/>
     </row>
     <row r="18" spans="1:20">
-      <c r="A18" s="18"/>
-      <c r="B18" s="19"/>
-      <c r="C18" s="19"/>
-      <c r="D18" s="19"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="19"/>
-      <c r="H18" s="19"/>
-      <c r="I18" s="19"/>
-      <c r="J18" s="19"/>
-      <c r="K18" s="19"/>
-      <c r="L18" s="19"/>
-      <c r="M18" s="19"/>
-      <c r="N18" s="19"/>
-      <c r="O18" s="19"/>
-      <c r="P18" s="19"/>
-      <c r="Q18" s="19"/>
-      <c r="R18" s="20"/>
+      <c r="A18" s="15"/>
+      <c r="B18" s="16"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="16"/>
+      <c r="H18" s="16"/>
+      <c r="I18" s="16"/>
+      <c r="J18" s="16"/>
+      <c r="K18" s="16"/>
+      <c r="L18" s="16"/>
+      <c r="M18" s="16"/>
+      <c r="N18" s="16"/>
+      <c r="O18" s="16"/>
+      <c r="P18" s="16"/>
+      <c r="Q18" s="16"/>
+      <c r="R18" s="17"/>
     </row>
     <row r="19" spans="1:20">
-      <c r="A19" s="18"/>
-      <c r="B19" s="19"/>
-      <c r="C19" s="19"/>
-      <c r="D19" s="19"/>
-      <c r="E19" s="19"/>
-      <c r="F19" s="19"/>
-      <c r="G19" s="19"/>
-      <c r="H19" s="19"/>
-      <c r="I19" s="19"/>
-      <c r="J19" s="19"/>
-      <c r="K19" s="19"/>
-      <c r="L19" s="19"/>
-      <c r="M19" s="19"/>
-      <c r="N19" s="19"/>
-      <c r="O19" s="19"/>
-      <c r="P19" s="19"/>
-      <c r="Q19" s="19"/>
-      <c r="R19" s="20"/>
+      <c r="A19" s="15"/>
+      <c r="B19" s="16"/>
+      <c r="C19" s="16"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="16"/>
+      <c r="F19" s="16"/>
+      <c r="G19" s="16"/>
+      <c r="H19" s="16"/>
+      <c r="I19" s="16"/>
+      <c r="J19" s="16"/>
+      <c r="K19" s="16"/>
+      <c r="L19" s="16"/>
+      <c r="M19" s="16"/>
+      <c r="N19" s="16"/>
+      <c r="O19" s="16"/>
+      <c r="P19" s="16"/>
+      <c r="Q19" s="16"/>
+      <c r="R19" s="17"/>
     </row>
     <row r="20" spans="1:20" ht="19.5">
-      <c r="A20" s="21" t="s">
+      <c r="A20" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="B20" s="22"/>
-      <c r="C20" s="22"/>
-      <c r="D20" s="22"/>
-      <c r="E20" s="22"/>
-      <c r="F20" s="22"/>
-      <c r="G20" s="22"/>
-      <c r="H20" s="22"/>
-      <c r="I20" s="22"/>
-      <c r="J20" s="22"/>
-      <c r="K20" s="22"/>
-      <c r="L20" s="22"/>
-      <c r="M20" s="22"/>
-      <c r="N20" s="22"/>
-      <c r="O20" s="22"/>
-      <c r="P20" s="22"/>
-      <c r="Q20" s="22"/>
-      <c r="R20" s="23"/>
+      <c r="B20" s="19"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="19"/>
+      <c r="H20" s="19"/>
+      <c r="I20" s="19"/>
+      <c r="J20" s="19"/>
+      <c r="K20" s="19"/>
+      <c r="L20" s="19"/>
+      <c r="M20" s="19"/>
+      <c r="N20" s="19"/>
+      <c r="O20" s="19"/>
+      <c r="P20" s="19"/>
+      <c r="Q20" s="19"/>
+      <c r="R20" s="20"/>
     </row>
     <row r="21" spans="1:20" ht="19.5">
-      <c r="A21" s="21"/>
-      <c r="B21" s="22"/>
-      <c r="C21" s="22"/>
-      <c r="D21" s="22"/>
-      <c r="E21" s="22"/>
-      <c r="F21" s="22"/>
-      <c r="G21" s="22"/>
-      <c r="H21" s="22"/>
-      <c r="I21" s="22"/>
-      <c r="J21" s="22"/>
-      <c r="K21" s="22"/>
-      <c r="L21" s="22"/>
-      <c r="M21" s="22"/>
-      <c r="N21" s="22"/>
-      <c r="O21" s="22"/>
-      <c r="P21" s="22"/>
-      <c r="Q21" s="22"/>
-      <c r="R21" s="23"/>
+      <c r="A21" s="18"/>
+      <c r="B21" s="19"/>
+      <c r="C21" s="19"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="19"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="19"/>
+      <c r="H21" s="19"/>
+      <c r="I21" s="19"/>
+      <c r="J21" s="19"/>
+      <c r="K21" s="19"/>
+      <c r="L21" s="19"/>
+      <c r="M21" s="19"/>
+      <c r="N21" s="19"/>
+      <c r="O21" s="19"/>
+      <c r="P21" s="19"/>
+      <c r="Q21" s="19"/>
+      <c r="R21" s="20"/>
     </row>
     <row r="22" spans="1:20" ht="19.5">
-      <c r="A22" s="21" t="s">
+      <c r="A22" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="B22" s="22"/>
-      <c r="C22" s="22"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="22"/>
-      <c r="F22" s="22"/>
-      <c r="G22" s="22"/>
-      <c r="H22" s="22"/>
-      <c r="I22" s="22"/>
-      <c r="J22" s="22"/>
-      <c r="K22" s="22"/>
-      <c r="L22" s="22"/>
-      <c r="M22" s="22"/>
-      <c r="N22" s="22"/>
-      <c r="O22" s="22"/>
-      <c r="P22" s="22"/>
-      <c r="Q22" s="22"/>
-      <c r="R22" s="23"/>
+      <c r="B22" s="19"/>
+      <c r="C22" s="19"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="19"/>
+      <c r="F22" s="19"/>
+      <c r="G22" s="19"/>
+      <c r="H22" s="19"/>
+      <c r="I22" s="19"/>
+      <c r="J22" s="19"/>
+      <c r="K22" s="19"/>
+      <c r="L22" s="19"/>
+      <c r="M22" s="19"/>
+      <c r="N22" s="19"/>
+      <c r="O22" s="19"/>
+      <c r="P22" s="19"/>
+      <c r="Q22" s="19"/>
+      <c r="R22" s="20"/>
     </row>
     <row r="23" spans="1:20" ht="19.5">
-      <c r="A23" s="21"/>
-      <c r="B23" s="22"/>
-      <c r="C23" s="22"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="22"/>
-      <c r="F23" s="22"/>
-      <c r="G23" s="22"/>
-      <c r="H23" s="22"/>
-      <c r="I23" s="22"/>
-      <c r="J23" s="22"/>
-      <c r="K23" s="22"/>
-      <c r="L23" s="22"/>
-      <c r="M23" s="22"/>
-      <c r="N23" s="22"/>
-      <c r="O23" s="22"/>
-      <c r="P23" s="22"/>
-      <c r="Q23" s="22"/>
-      <c r="R23" s="23"/>
+      <c r="A23" s="18"/>
+      <c r="B23" s="19"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="19"/>
+      <c r="G23" s="19"/>
+      <c r="H23" s="19"/>
+      <c r="I23" s="19"/>
+      <c r="J23" s="19"/>
+      <c r="K23" s="19"/>
+      <c r="L23" s="19"/>
+      <c r="M23" s="19"/>
+      <c r="N23" s="19"/>
+      <c r="O23" s="19"/>
+      <c r="P23" s="19"/>
+      <c r="Q23" s="19"/>
+      <c r="R23" s="20"/>
     </row>
     <row r="24" spans="1:20" ht="19.5">
-      <c r="A24" s="21" t="s">
+      <c r="A24" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B24" s="22"/>
-      <c r="C24" s="22"/>
-      <c r="D24" s="22"/>
-      <c r="E24" s="22"/>
-      <c r="F24" s="22"/>
-      <c r="G24" s="22"/>
-      <c r="H24" s="22"/>
-      <c r="I24" s="22"/>
-      <c r="J24" s="22"/>
-      <c r="K24" s="22"/>
-      <c r="L24" s="22"/>
-      <c r="M24" s="22"/>
-      <c r="N24" s="22"/>
-      <c r="O24" s="22"/>
-      <c r="P24" s="22"/>
-      <c r="Q24" s="22"/>
-      <c r="R24" s="23"/>
+      <c r="B24" s="19"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="19"/>
+      <c r="H24" s="19"/>
+      <c r="I24" s="19"/>
+      <c r="J24" s="19"/>
+      <c r="K24" s="19"/>
+      <c r="L24" s="19"/>
+      <c r="M24" s="19"/>
+      <c r="N24" s="19"/>
+      <c r="O24" s="19"/>
+      <c r="P24" s="19"/>
+      <c r="Q24" s="19"/>
+      <c r="R24" s="20"/>
     </row>
     <row r="25" spans="1:20" ht="19.5">
-      <c r="A25" s="21"/>
-      <c r="B25" s="22"/>
-      <c r="C25" s="22"/>
-      <c r="D25" s="22"/>
-      <c r="E25" s="22"/>
-      <c r="F25" s="22"/>
-      <c r="G25" s="22"/>
-      <c r="H25" s="22"/>
-      <c r="I25" s="22"/>
-      <c r="J25" s="22"/>
-      <c r="K25" s="22"/>
-      <c r="L25" s="22"/>
-      <c r="M25" s="22"/>
-      <c r="N25" s="22"/>
-      <c r="O25" s="22"/>
-      <c r="P25" s="22"/>
-      <c r="Q25" s="22"/>
-      <c r="R25" s="23"/>
+      <c r="A25" s="18"/>
+      <c r="B25" s="19"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="19"/>
+      <c r="J25" s="19"/>
+      <c r="K25" s="19"/>
+      <c r="L25" s="19"/>
+      <c r="M25" s="19"/>
+      <c r="N25" s="19"/>
+      <c r="O25" s="19"/>
+      <c r="P25" s="19"/>
+      <c r="Q25" s="19"/>
+      <c r="R25" s="20"/>
       <c r="S25" t="s">
         <v>0</v>
       </c>
@@ -1532,76 +1509,76 @@
       </c>
     </row>
     <row r="26" spans="1:20" ht="19.5">
-      <c r="A26" s="21"/>
-      <c r="B26" s="22"/>
-      <c r="C26" s="22"/>
-      <c r="D26" s="22"/>
-      <c r="E26" s="22" t="s">
+      <c r="A26" s="18"/>
+      <c r="B26" s="19"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="F26" s="22"/>
-      <c r="G26" s="22"/>
-      <c r="H26" s="22"/>
-      <c r="I26" s="22"/>
-      <c r="J26" s="22"/>
-      <c r="K26" s="22"/>
-      <c r="L26" s="22"/>
-      <c r="M26" s="22"/>
-      <c r="N26" s="22"/>
-      <c r="O26" s="22"/>
-      <c r="P26" s="22"/>
-      <c r="Q26" s="22"/>
-      <c r="R26" s="23"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="19"/>
+      <c r="I26" s="19"/>
+      <c r="J26" s="19"/>
+      <c r="K26" s="19"/>
+      <c r="L26" s="19"/>
+      <c r="M26" s="19"/>
+      <c r="N26" s="19"/>
+      <c r="O26" s="19"/>
+      <c r="P26" s="19"/>
+      <c r="Q26" s="19"/>
+      <c r="R26" s="20"/>
     </row>
     <row r="27" spans="1:20" ht="19.5">
-      <c r="A27" s="21"/>
-      <c r="B27" s="22"/>
-      <c r="C27" s="22"/>
-      <c r="D27" s="22"/>
-      <c r="E27" s="22"/>
-      <c r="F27" s="24"/>
-      <c r="G27" s="24"/>
-      <c r="H27" s="24"/>
-      <c r="I27" s="22"/>
-      <c r="J27" s="22"/>
-      <c r="K27" s="22"/>
-      <c r="L27" s="22"/>
-      <c r="M27" s="22"/>
-      <c r="N27" s="22"/>
-      <c r="O27" s="22"/>
-      <c r="P27" s="22"/>
-      <c r="Q27" s="22"/>
-      <c r="R27" s="23"/>
+      <c r="A27" s="18"/>
+      <c r="B27" s="19"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="21"/>
+      <c r="G27" s="21"/>
+      <c r="H27" s="21"/>
+      <c r="I27" s="19"/>
+      <c r="J27" s="19"/>
+      <c r="K27" s="19"/>
+      <c r="L27" s="19"/>
+      <c r="M27" s="19"/>
+      <c r="N27" s="19"/>
+      <c r="O27" s="19"/>
+      <c r="P27" s="19"/>
+      <c r="Q27" s="19"/>
+      <c r="R27" s="20"/>
     </row>
     <row r="28" spans="1:20" ht="19.5">
-      <c r="A28" s="40" t="s">
+      <c r="A28" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="B28" s="41"/>
-      <c r="C28" s="25"/>
-      <c r="D28" s="25"/>
-      <c r="E28" s="29"/>
-      <c r="F28" s="30"/>
-      <c r="G28" s="30"/>
-      <c r="H28" s="25" t="s">
+      <c r="B28" s="30"/>
+      <c r="C28" s="22"/>
+      <c r="D28" s="22"/>
+      <c r="E28" s="27"/>
+      <c r="F28" s="28"/>
+      <c r="G28" s="28"/>
+      <c r="H28" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="I28" s="29"/>
-      <c r="J28" s="30"/>
-      <c r="K28" s="30"/>
-      <c r="L28" s="25" t="s">
+      <c r="I28" s="27"/>
+      <c r="J28" s="28"/>
+      <c r="K28" s="28"/>
+      <c r="L28" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="M28" s="30"/>
-      <c r="N28" s="30"/>
-      <c r="O28" s="30"/>
-      <c r="P28" s="28" t="s">
+      <c r="M28" s="28"/>
+      <c r="N28" s="28"/>
+      <c r="O28" s="28"/>
+      <c r="P28" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="Q28" s="26" t="s">
-        <v>0</v>
-      </c>
-      <c r="R28" s="27"/>
+      <c r="Q28" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="R28" s="24"/>
     </row>
     <row r="29" spans="1:20" s="1" customFormat="1" ht="21">
       <c r="O29" s="6" t="s">
@@ -1609,12 +1586,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="A1:R1"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:R4"/>
-    <mergeCell ref="B2:R2"/>
-    <mergeCell ref="B3:R3"/>
+  <mergeCells count="17">
     <mergeCell ref="E28:G28"/>
     <mergeCell ref="I28:K28"/>
     <mergeCell ref="A5:B5"/>
@@ -1625,6 +1597,13 @@
     <mergeCell ref="A13:R13"/>
     <mergeCell ref="A28:B28"/>
     <mergeCell ref="M28:O28"/>
+    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:R4"/>
+    <mergeCell ref="C2:R2"/>
+    <mergeCell ref="C3:R3"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="0.45" bottom="0.41" header="0.48" footer="0.5"/>

--- a/NT_AirPollution.Web/App_Data/Payment/Template/結清證明.xlsx
+++ b/NT_AirPollution.Web/App_Data/Payment/Template/結清證明.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\owner\Desktop\暫時\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\case\Alvin\NT_AirPollution\NT_AirPollution.Web\App_Data\Payment\Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC284FAF-C3BB-40FF-870F-5053B8166467}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3531370-6662-4B33-AA44-2BC39C97D15E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="14160" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="結清證明" sheetId="60" r:id="rId1"/>
@@ -306,7 +306,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -365,65 +365,68 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -800,138 +803,138 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="34.35" customHeight="1">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
-      <c r="K1" s="26"/>
-      <c r="L1" s="26"/>
-      <c r="M1" s="26"/>
-      <c r="N1" s="26"/>
-      <c r="O1" s="26"/>
-      <c r="P1" s="26"/>
-      <c r="Q1" s="26"/>
-      <c r="R1" s="26"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
+      <c r="K1" s="38"/>
+      <c r="L1" s="38"/>
+      <c r="M1" s="38"/>
+      <c r="N1" s="38"/>
+      <c r="O1" s="38"/>
+      <c r="P1" s="38"/>
+      <c r="Q1" s="38"/>
+      <c r="R1" s="38"/>
       <c r="S1" s="10"/>
     </row>
-    <row r="2" spans="1:20" s="10" customFormat="1" ht="34.35" customHeight="1">
-      <c r="A2" s="36" t="s">
+    <row r="2" spans="1:20" s="10" customFormat="1" ht="39.950000000000003" customHeight="1">
+      <c r="A2" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="37"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
-      <c r="I2" s="38"/>
-      <c r="J2" s="38"/>
-      <c r="K2" s="38"/>
-      <c r="L2" s="38"/>
-      <c r="M2" s="38"/>
-      <c r="N2" s="38"/>
-      <c r="O2" s="38"/>
-      <c r="P2" s="38"/>
-      <c r="Q2" s="38"/>
-      <c r="R2" s="39"/>
+      <c r="B2" s="46"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="41"/>
+      <c r="J2" s="41"/>
+      <c r="K2" s="41"/>
+      <c r="L2" s="41"/>
+      <c r="M2" s="41"/>
+      <c r="N2" s="41"/>
+      <c r="O2" s="41"/>
+      <c r="P2" s="41"/>
+      <c r="Q2" s="41"/>
+      <c r="R2" s="42"/>
       <c r="S2" s="9"/>
     </row>
     <row r="3" spans="1:20" s="9" customFormat="1" ht="34.35" customHeight="1">
-      <c r="A3" s="40" t="s">
+      <c r="A3" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="41"/>
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="42"/>
-      <c r="H3" s="42"/>
-      <c r="I3" s="42"/>
-      <c r="J3" s="42"/>
-      <c r="K3" s="42"/>
-      <c r="L3" s="42"/>
-      <c r="M3" s="42"/>
-      <c r="N3" s="42"/>
-      <c r="O3" s="42"/>
-      <c r="P3" s="42"/>
-      <c r="Q3" s="42"/>
-      <c r="R3" s="43"/>
-    </row>
-    <row r="4" spans="1:20" s="9" customFormat="1" ht="34.35" customHeight="1">
-      <c r="A4" s="40" t="s">
+      <c r="B3" s="31"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="43"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="43"/>
+      <c r="I3" s="43"/>
+      <c r="J3" s="43"/>
+      <c r="K3" s="43"/>
+      <c r="L3" s="43"/>
+      <c r="M3" s="43"/>
+      <c r="N3" s="43"/>
+      <c r="O3" s="43"/>
+      <c r="P3" s="43"/>
+      <c r="Q3" s="43"/>
+      <c r="R3" s="44"/>
+    </row>
+    <row r="4" spans="1:20" s="9" customFormat="1" ht="68.099999999999994" customHeight="1">
+      <c r="A4" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="44"/>
-      <c r="C4" s="44"/>
-      <c r="D4" s="44"/>
-      <c r="E4" s="44"/>
-      <c r="F4" s="44"/>
-      <c r="G4" s="44"/>
-      <c r="H4" s="44"/>
-      <c r="I4" s="44"/>
-      <c r="J4" s="44"/>
-      <c r="K4" s="44"/>
-      <c r="L4" s="44"/>
-      <c r="M4" s="44"/>
-      <c r="N4" s="44"/>
-      <c r="O4" s="44"/>
-      <c r="P4" s="44"/>
-      <c r="Q4" s="44"/>
-      <c r="R4" s="45"/>
+      <c r="B4" s="31"/>
+      <c r="C4" s="39"/>
+      <c r="D4" s="39"/>
+      <c r="E4" s="39"/>
+      <c r="F4" s="39"/>
+      <c r="G4" s="39"/>
+      <c r="H4" s="39"/>
+      <c r="I4" s="39"/>
+      <c r="J4" s="39"/>
+      <c r="K4" s="39"/>
+      <c r="L4" s="39"/>
+      <c r="M4" s="39"/>
+      <c r="N4" s="39"/>
+      <c r="O4" s="39"/>
+      <c r="P4" s="39"/>
+      <c r="Q4" s="39"/>
+      <c r="R4" s="40"/>
     </row>
     <row r="5" spans="1:20" s="9" customFormat="1" ht="34.35" customHeight="1">
-      <c r="A5" s="40" t="s">
+      <c r="A5" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="44"/>
-      <c r="C5" s="44"/>
-      <c r="D5" s="44"/>
-      <c r="E5" s="44"/>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44"/>
-      <c r="H5" s="44"/>
-      <c r="I5" s="44"/>
-      <c r="J5" s="44"/>
-      <c r="K5" s="44"/>
-      <c r="L5" s="44"/>
-      <c r="M5" s="44"/>
-      <c r="N5" s="44"/>
-      <c r="O5" s="44"/>
-      <c r="P5" s="44"/>
-      <c r="Q5" s="44"/>
-      <c r="R5" s="45"/>
+      <c r="B5" s="31"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="31"/>
+      <c r="F5" s="31"/>
+      <c r="G5" s="31"/>
+      <c r="H5" s="31"/>
+      <c r="I5" s="31"/>
+      <c r="J5" s="31"/>
+      <c r="K5" s="31"/>
+      <c r="L5" s="31"/>
+      <c r="M5" s="31"/>
+      <c r="N5" s="31"/>
+      <c r="O5" s="31"/>
+      <c r="P5" s="31"/>
+      <c r="Q5" s="31"/>
+      <c r="R5" s="32"/>
     </row>
     <row r="6" spans="1:20" s="9" customFormat="1" ht="34.35" customHeight="1">
-      <c r="A6" s="40" t="s">
+      <c r="A6" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="44"/>
-      <c r="C6" s="44"/>
-      <c r="D6" s="44"/>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="44"/>
-      <c r="H6" s="44"/>
-      <c r="I6" s="44"/>
-      <c r="J6" s="44"/>
-      <c r="K6" s="44"/>
-      <c r="L6" s="44"/>
-      <c r="M6" s="44"/>
-      <c r="N6" s="44"/>
-      <c r="O6" s="44"/>
-      <c r="P6" s="44"/>
-      <c r="Q6" s="44"/>
-      <c r="R6" s="45"/>
+      <c r="B6" s="31"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="31"/>
+      <c r="G6" s="31"/>
+      <c r="H6" s="31"/>
+      <c r="I6" s="31"/>
+      <c r="J6" s="31"/>
+      <c r="K6" s="31"/>
+      <c r="L6" s="31"/>
+      <c r="M6" s="31"/>
+      <c r="N6" s="31"/>
+      <c r="O6" s="31"/>
+      <c r="P6" s="31"/>
+      <c r="Q6" s="31"/>
+      <c r="R6" s="32"/>
     </row>
     <row r="7" spans="1:20" ht="35.1" customHeight="1">
       <c r="A7" s="4"/>
@@ -954,29 +957,29 @@
       <c r="R7" s="3"/>
     </row>
     <row r="8" spans="1:20" ht="35.1" customHeight="1">
-      <c r="A8" s="31" t="s">
+      <c r="A8" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="32"/>
-      <c r="C8" s="32"/>
-      <c r="D8" s="32"/>
-      <c r="E8" s="32"/>
-      <c r="F8" s="32"/>
-      <c r="G8" s="32"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
-      <c r="J8" s="32"/>
-      <c r="K8" s="32"/>
-      <c r="L8" s="32"/>
-      <c r="M8" s="32"/>
-      <c r="N8" s="32"/>
-      <c r="O8" s="32"/>
-      <c r="P8" s="32"/>
-      <c r="Q8" s="32"/>
-      <c r="R8" s="33"/>
+      <c r="B8" s="34"/>
+      <c r="C8" s="34"/>
+      <c r="D8" s="34"/>
+      <c r="E8" s="34"/>
+      <c r="F8" s="34"/>
+      <c r="G8" s="34"/>
+      <c r="H8" s="34"/>
+      <c r="I8" s="34"/>
+      <c r="J8" s="34"/>
+      <c r="K8" s="34"/>
+      <c r="L8" s="34"/>
+      <c r="M8" s="34"/>
+      <c r="N8" s="34"/>
+      <c r="O8" s="34"/>
+      <c r="P8" s="34"/>
+      <c r="Q8" s="34"/>
+      <c r="R8" s="35"/>
     </row>
     <row r="9" spans="1:20" s="8" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A9" s="34" t="s">
+      <c r="A9" s="27" t="s">
         <v>7</v>
       </c>
       <c r="B9" s="13">
@@ -1032,7 +1035,7 @@
       </c>
     </row>
     <row r="10" spans="1:20" s="8" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A10" s="34" t="s">
+      <c r="A10" s="27" t="s">
         <v>13</v>
       </c>
       <c r="B10" s="13">
@@ -1088,7 +1091,7 @@
       </c>
     </row>
     <row r="11" spans="1:20" s="8" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A11" s="34" t="s">
+      <c r="A11" s="27" t="s">
         <v>14</v>
       </c>
       <c r="B11" s="13">
@@ -1144,7 +1147,7 @@
       </c>
     </row>
     <row r="12" spans="1:20" s="8" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A12" s="34" t="s">
+      <c r="A12" s="27" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="13">
@@ -1203,27 +1206,27 @@
       </c>
     </row>
     <row r="13" spans="1:20" s="8" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A13" s="31"/>
-      <c r="B13" s="32"/>
-      <c r="C13" s="32"/>
-      <c r="D13" s="32"/>
-      <c r="E13" s="32"/>
-      <c r="F13" s="32"/>
-      <c r="G13" s="32"/>
-      <c r="H13" s="32"/>
-      <c r="I13" s="32"/>
-      <c r="J13" s="32"/>
-      <c r="K13" s="32"/>
-      <c r="L13" s="32"/>
-      <c r="M13" s="32"/>
-      <c r="N13" s="32"/>
-      <c r="O13" s="32"/>
-      <c r="P13" s="32"/>
-      <c r="Q13" s="32"/>
-      <c r="R13" s="33"/>
+      <c r="A13" s="33"/>
+      <c r="B13" s="34"/>
+      <c r="C13" s="34"/>
+      <c r="D13" s="34"/>
+      <c r="E13" s="34"/>
+      <c r="F13" s="34"/>
+      <c r="G13" s="34"/>
+      <c r="H13" s="34"/>
+      <c r="I13" s="34"/>
+      <c r="J13" s="34"/>
+      <c r="K13" s="34"/>
+      <c r="L13" s="34"/>
+      <c r="M13" s="34"/>
+      <c r="N13" s="34"/>
+      <c r="O13" s="34"/>
+      <c r="P13" s="34"/>
+      <c r="Q13" s="34"/>
+      <c r="R13" s="35"/>
     </row>
     <row r="14" spans="1:20" s="8" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A14" s="35"/>
+      <c r="A14" s="26"/>
       <c r="B14" s="13">
         <v>0</v>
       </c>
@@ -1551,27 +1554,27 @@
       <c r="R27" s="20"/>
     </row>
     <row r="28" spans="1:20" ht="19.5">
-      <c r="A28" s="29" t="s">
+      <c r="A28" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="B28" s="30"/>
+      <c r="B28" s="37"/>
       <c r="C28" s="22"/>
       <c r="D28" s="22"/>
-      <c r="E28" s="27"/>
-      <c r="F28" s="28"/>
-      <c r="G28" s="28"/>
+      <c r="E28" s="28"/>
+      <c r="F28" s="29"/>
+      <c r="G28" s="29"/>
       <c r="H28" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="I28" s="27"/>
-      <c r="J28" s="28"/>
-      <c r="K28" s="28"/>
+      <c r="I28" s="28"/>
+      <c r="J28" s="29"/>
+      <c r="K28" s="29"/>
       <c r="L28" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="M28" s="28"/>
-      <c r="N28" s="28"/>
-      <c r="O28" s="28"/>
+      <c r="M28" s="29"/>
+      <c r="N28" s="29"/>
+      <c r="O28" s="29"/>
       <c r="P28" s="25" t="s">
         <v>25</v>
       </c>
@@ -1587,6 +1590,13 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:R4"/>
+    <mergeCell ref="C2:R2"/>
+    <mergeCell ref="C3:R3"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
     <mergeCell ref="E28:G28"/>
     <mergeCell ref="I28:K28"/>
     <mergeCell ref="A5:B5"/>
@@ -1597,13 +1607,6 @@
     <mergeCell ref="A13:R13"/>
     <mergeCell ref="A28:B28"/>
     <mergeCell ref="M28:O28"/>
-    <mergeCell ref="A1:R1"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:R4"/>
-    <mergeCell ref="C2:R2"/>
-    <mergeCell ref="C3:R3"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B3"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="0.45" bottom="0.41" header="0.48" footer="0.5"/>

--- a/NT_AirPollution.Web/App_Data/Payment/Template/結清證明.xlsx
+++ b/NT_AirPollution.Web/App_Data/Payment/Template/結清證明.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\case\Alvin\NT_AirPollution\NT_AirPollution.Web\App_Data\Payment\Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3531370-6662-4B33-AA44-2BC39C97D15E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F60CE23C-AA05-4740-B9A9-6753A6172254}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="14160" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="結清證明" sheetId="60" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="ccc">#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">結清證明!$A$1:$R$28</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">結清證明!$A$1:$R$29</definedName>
     <definedName name="www">#REF!</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="28">
   <si>
     <t xml:space="preserve"> </t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -132,6 +132,10 @@
   </si>
   <si>
     <t>南投縣政府環境保護局</t>
+  </si>
+  <si>
+    <t xml:space="preserve">該工程已完全結清應繳費額,共計:                     </t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -306,7 +310,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -371,18 +375,45 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -401,33 +432,12 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -451,13 +461,13 @@
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>13607</xdr:colOff>
-      <xdr:row>18</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>149678</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
       <xdr:colOff>27387</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>122463</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -795,146 +805,146 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:T29"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <dimension ref="A1:T30"/>
+  <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
-    <col min="1" max="1" width="15.875" customWidth="1"/>
-    <col min="2" max="18" width="4.125" customWidth="1"/>
+    <col min="1" max="1" width="15.88671875" customWidth="1"/>
+    <col min="2" max="18" width="4.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="34.35" customHeight="1">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
-      <c r="J1" s="38"/>
-      <c r="K1" s="38"/>
-      <c r="L1" s="38"/>
-      <c r="M1" s="38"/>
-      <c r="N1" s="38"/>
-      <c r="O1" s="38"/>
-      <c r="P1" s="38"/>
-      <c r="Q1" s="38"/>
-      <c r="R1" s="38"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
+      <c r="M1" s="28"/>
+      <c r="N1" s="28"/>
+      <c r="O1" s="28"/>
+      <c r="P1" s="28"/>
+      <c r="Q1" s="28"/>
+      <c r="R1" s="28"/>
       <c r="S1" s="10"/>
     </row>
-    <row r="2" spans="1:20" s="10" customFormat="1" ht="39.950000000000003" customHeight="1">
-      <c r="A2" s="45" t="s">
+    <row r="2" spans="1:20" s="10" customFormat="1" ht="39.9" customHeight="1">
+      <c r="A2" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="46"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
-      <c r="J2" s="41"/>
-      <c r="K2" s="41"/>
-      <c r="L2" s="41"/>
-      <c r="M2" s="41"/>
-      <c r="N2" s="41"/>
-      <c r="O2" s="41"/>
-      <c r="P2" s="41"/>
-      <c r="Q2" s="41"/>
-      <c r="R2" s="42"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
+      <c r="J2" s="33"/>
+      <c r="K2" s="33"/>
+      <c r="L2" s="33"/>
+      <c r="M2" s="33"/>
+      <c r="N2" s="33"/>
+      <c r="O2" s="33"/>
+      <c r="P2" s="33"/>
+      <c r="Q2" s="33"/>
+      <c r="R2" s="34"/>
       <c r="S2" s="9"/>
     </row>
     <row r="3" spans="1:20" s="9" customFormat="1" ht="34.35" customHeight="1">
-      <c r="A3" s="30" t="s">
+      <c r="A3" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="31"/>
-      <c r="C3" s="43"/>
-      <c r="D3" s="43"/>
-      <c r="E3" s="43"/>
-      <c r="F3" s="43"/>
-      <c r="G3" s="43"/>
-      <c r="H3" s="43"/>
-      <c r="I3" s="43"/>
-      <c r="J3" s="43"/>
-      <c r="K3" s="43"/>
-      <c r="L3" s="43"/>
-      <c r="M3" s="43"/>
-      <c r="N3" s="43"/>
-      <c r="O3" s="43"/>
-      <c r="P3" s="43"/>
-      <c r="Q3" s="43"/>
-      <c r="R3" s="44"/>
+      <c r="B3" s="30"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="35"/>
+      <c r="H3" s="35"/>
+      <c r="I3" s="35"/>
+      <c r="J3" s="35"/>
+      <c r="K3" s="35"/>
+      <c r="L3" s="35"/>
+      <c r="M3" s="35"/>
+      <c r="N3" s="35"/>
+      <c r="O3" s="35"/>
+      <c r="P3" s="35"/>
+      <c r="Q3" s="35"/>
+      <c r="R3" s="36"/>
     </row>
     <row r="4" spans="1:20" s="9" customFormat="1" ht="68.099999999999994" customHeight="1">
-      <c r="A4" s="30" t="s">
+      <c r="A4" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="31"/>
-      <c r="C4" s="39"/>
-      <c r="D4" s="39"/>
-      <c r="E4" s="39"/>
-      <c r="F4" s="39"/>
-      <c r="G4" s="39"/>
-      <c r="H4" s="39"/>
-      <c r="I4" s="39"/>
-      <c r="J4" s="39"/>
-      <c r="K4" s="39"/>
-      <c r="L4" s="39"/>
-      <c r="M4" s="39"/>
-      <c r="N4" s="39"/>
-      <c r="O4" s="39"/>
-      <c r="P4" s="39"/>
-      <c r="Q4" s="39"/>
-      <c r="R4" s="40"/>
+      <c r="B4" s="30"/>
+      <c r="C4" s="31"/>
+      <c r="D4" s="31"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="31"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="31"/>
+      <c r="I4" s="31"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="31"/>
+      <c r="M4" s="31"/>
+      <c r="N4" s="31"/>
+      <c r="O4" s="31"/>
+      <c r="P4" s="31"/>
+      <c r="Q4" s="31"/>
+      <c r="R4" s="32"/>
     </row>
     <row r="5" spans="1:20" s="9" customFormat="1" ht="34.35" customHeight="1">
-      <c r="A5" s="30" t="s">
+      <c r="A5" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="31"/>
-      <c r="C5" s="31"/>
-      <c r="D5" s="31"/>
-      <c r="E5" s="31"/>
-      <c r="F5" s="31"/>
-      <c r="G5" s="31"/>
-      <c r="H5" s="31"/>
-      <c r="I5" s="31"/>
-      <c r="J5" s="31"/>
-      <c r="K5" s="31"/>
-      <c r="L5" s="31"/>
-      <c r="M5" s="31"/>
-      <c r="N5" s="31"/>
-      <c r="O5" s="31"/>
-      <c r="P5" s="31"/>
-      <c r="Q5" s="31"/>
-      <c r="R5" s="32"/>
+      <c r="B5" s="30"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="30"/>
+      <c r="E5" s="30"/>
+      <c r="F5" s="30"/>
+      <c r="G5" s="30"/>
+      <c r="H5" s="30"/>
+      <c r="I5" s="30"/>
+      <c r="J5" s="30"/>
+      <c r="K5" s="30"/>
+      <c r="L5" s="30"/>
+      <c r="M5" s="30"/>
+      <c r="N5" s="30"/>
+      <c r="O5" s="30"/>
+      <c r="P5" s="30"/>
+      <c r="Q5" s="30"/>
+      <c r="R5" s="41"/>
     </row>
     <row r="6" spans="1:20" s="9" customFormat="1" ht="34.35" customHeight="1">
-      <c r="A6" s="30" t="s">
+      <c r="A6" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="31"/>
-      <c r="C6" s="31"/>
-      <c r="D6" s="31"/>
-      <c r="E6" s="31"/>
-      <c r="F6" s="31"/>
-      <c r="G6" s="31"/>
-      <c r="H6" s="31"/>
-      <c r="I6" s="31"/>
-      <c r="J6" s="31"/>
-      <c r="K6" s="31"/>
-      <c r="L6" s="31"/>
-      <c r="M6" s="31"/>
-      <c r="N6" s="31"/>
-      <c r="O6" s="31"/>
-      <c r="P6" s="31"/>
-      <c r="Q6" s="31"/>
-      <c r="R6" s="32"/>
+      <c r="B6" s="30"/>
+      <c r="C6" s="30"/>
+      <c r="D6" s="30"/>
+      <c r="E6" s="30"/>
+      <c r="F6" s="30"/>
+      <c r="G6" s="30"/>
+      <c r="H6" s="30"/>
+      <c r="I6" s="30"/>
+      <c r="J6" s="30"/>
+      <c r="K6" s="30"/>
+      <c r="L6" s="30"/>
+      <c r="M6" s="30"/>
+      <c r="N6" s="30"/>
+      <c r="O6" s="30"/>
+      <c r="P6" s="30"/>
+      <c r="Q6" s="30"/>
+      <c r="R6" s="41"/>
     </row>
     <row r="7" spans="1:20" ht="35.1" customHeight="1">
       <c r="A7" s="4"/>
@@ -957,26 +967,26 @@
       <c r="R7" s="3"/>
     </row>
     <row r="8" spans="1:20" ht="35.1" customHeight="1">
-      <c r="A8" s="33" t="s">
+      <c r="A8" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="34"/>
-      <c r="C8" s="34"/>
-      <c r="D8" s="34"/>
-      <c r="E8" s="34"/>
-      <c r="F8" s="34"/>
-      <c r="G8" s="34"/>
-      <c r="H8" s="34"/>
-      <c r="I8" s="34"/>
-      <c r="J8" s="34"/>
-      <c r="K8" s="34"/>
-      <c r="L8" s="34"/>
-      <c r="M8" s="34"/>
-      <c r="N8" s="34"/>
-      <c r="O8" s="34"/>
-      <c r="P8" s="34"/>
-      <c r="Q8" s="34"/>
-      <c r="R8" s="35"/>
+      <c r="B8" s="43"/>
+      <c r="C8" s="43"/>
+      <c r="D8" s="43"/>
+      <c r="E8" s="43"/>
+      <c r="F8" s="43"/>
+      <c r="G8" s="43"/>
+      <c r="H8" s="43"/>
+      <c r="I8" s="43"/>
+      <c r="J8" s="43"/>
+      <c r="K8" s="43"/>
+      <c r="L8" s="43"/>
+      <c r="M8" s="43"/>
+      <c r="N8" s="43"/>
+      <c r="O8" s="43"/>
+      <c r="P8" s="43"/>
+      <c r="Q8" s="43"/>
+      <c r="R8" s="44"/>
     </row>
     <row r="9" spans="1:20" s="8" customFormat="1" ht="35.1" customHeight="1">
       <c r="A9" s="27" t="s">
@@ -1091,64 +1101,28 @@
       </c>
     </row>
     <row r="11" spans="1:20" s="8" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A11" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" s="13">
-        <v>0</v>
-      </c>
-      <c r="C11" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="D11" s="13">
-        <v>0</v>
-      </c>
-      <c r="E11" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" s="13">
-        <v>0</v>
-      </c>
-      <c r="G11" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="H11" s="13">
-        <v>0</v>
-      </c>
-      <c r="I11" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="J11" s="13">
-        <v>0</v>
-      </c>
-      <c r="K11" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="L11" s="13">
-        <v>0</v>
-      </c>
-      <c r="M11" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="N11" s="13">
-        <v>0</v>
-      </c>
-      <c r="O11" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="P11" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="R11" s="14" t="s">
-        <v>12</v>
-      </c>
+      <c r="A11" s="47"/>
+      <c r="B11" s="50"/>
+      <c r="C11" s="50"/>
+      <c r="D11" s="50"/>
+      <c r="E11" s="50"/>
+      <c r="F11" s="50"/>
+      <c r="G11" s="50"/>
+      <c r="H11" s="50"/>
+      <c r="I11" s="50"/>
+      <c r="J11" s="50"/>
+      <c r="K11" s="50"/>
+      <c r="L11" s="50"/>
+      <c r="M11" s="50"/>
+      <c r="N11" s="50"/>
+      <c r="O11" s="50"/>
+      <c r="P11" s="50"/>
+      <c r="Q11" s="50"/>
+      <c r="R11" s="48"/>
     </row>
     <row r="12" spans="1:20" s="8" customFormat="1" ht="35.1" customHeight="1">
       <c r="A12" s="27" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B12" s="13">
         <v>0</v>
@@ -1201,125 +1175,163 @@
       <c r="R12" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="T12" s="11" t="s">
+    </row>
+    <row r="13" spans="1:20" s="8" customFormat="1" ht="35.1" customHeight="1">
+      <c r="A13" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="13">
+        <v>0</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="13">
+        <v>0</v>
+      </c>
+      <c r="E13" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" s="13">
+        <v>0</v>
+      </c>
+      <c r="G13" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="H13" s="13">
+        <v>0</v>
+      </c>
+      <c r="I13" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="J13" s="13">
+        <v>0</v>
+      </c>
+      <c r="K13" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="L13" s="13">
+        <v>0</v>
+      </c>
+      <c r="M13" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="N13" s="13">
+        <v>0</v>
+      </c>
+      <c r="O13" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="P13" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="R13" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="T13" s="11" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:20" s="8" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A13" s="33"/>
-      <c r="B13" s="34"/>
-      <c r="C13" s="34"/>
-      <c r="D13" s="34"/>
-      <c r="E13" s="34"/>
-      <c r="F13" s="34"/>
-      <c r="G13" s="34"/>
-      <c r="H13" s="34"/>
-      <c r="I13" s="34"/>
-      <c r="J13" s="34"/>
-      <c r="K13" s="34"/>
-      <c r="L13" s="34"/>
-      <c r="M13" s="34"/>
-      <c r="N13" s="34"/>
-      <c r="O13" s="34"/>
-      <c r="P13" s="34"/>
-      <c r="Q13" s="34"/>
-      <c r="R13" s="35"/>
-    </row>
     <row r="14" spans="1:20" s="8" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A14" s="26"/>
-      <c r="B14" s="13">
-        <v>0</v>
-      </c>
-      <c r="C14" s="13" t="s">
+      <c r="A14" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" s="49"/>
+      <c r="C14" s="49"/>
+      <c r="D14" s="49"/>
+      <c r="E14" s="49"/>
+      <c r="F14" s="49"/>
+      <c r="G14" s="49"/>
+      <c r="H14" s="49"/>
+      <c r="I14" s="49"/>
+      <c r="J14" s="49"/>
+      <c r="K14" s="49"/>
+      <c r="L14" s="49"/>
+      <c r="M14" s="49"/>
+      <c r="N14" s="49"/>
+      <c r="O14" s="49"/>
+      <c r="P14" s="49"/>
+      <c r="Q14" s="49"/>
+      <c r="R14" s="44"/>
+    </row>
+    <row r="15" spans="1:20" s="8" customFormat="1" ht="35.1" customHeight="1">
+      <c r="A15" s="26"/>
+      <c r="B15" s="13">
+        <v>0</v>
+      </c>
+      <c r="C15" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="D14" s="13">
-        <v>0</v>
-      </c>
-      <c r="E14" s="13" t="s">
+      <c r="D15" s="13">
+        <v>0</v>
+      </c>
+      <c r="E15" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="F14" s="13">
-        <v>0</v>
-      </c>
-      <c r="G14" s="13" t="s">
+      <c r="F15" s="13">
+        <v>0</v>
+      </c>
+      <c r="G15" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="H14" s="13">
-        <v>0</v>
-      </c>
-      <c r="I14" s="13" t="s">
+      <c r="H15" s="13">
+        <v>0</v>
+      </c>
+      <c r="I15" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="J14" s="13">
-        <v>0</v>
-      </c>
-      <c r="K14" s="13" t="s">
+      <c r="J15" s="13">
+        <v>0</v>
+      </c>
+      <c r="K15" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="13">
-        <v>0</v>
-      </c>
-      <c r="M14" s="13" t="s">
+      <c r="L15" s="13">
+        <v>0</v>
+      </c>
+      <c r="M15" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="N14" s="13">
-        <v>0</v>
-      </c>
-      <c r="O14" s="13" t="s">
+      <c r="N15" s="13">
+        <v>0</v>
+      </c>
+      <c r="O15" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="P14" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="13" t="s">
+      <c r="P15" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="R14" s="14" t="s">
+      <c r="R15" s="14" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:20" s="8" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A15" s="12"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="13"/>
-      <c r="H15" s="7"/>
-      <c r="I15" s="13"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="13"/>
-      <c r="L15" s="7"/>
-      <c r="M15" s="13"/>
-      <c r="N15" s="7"/>
-      <c r="O15" s="13"/>
-      <c r="P15" s="7"/>
-      <c r="Q15" s="13"/>
-      <c r="R15" s="14"/>
-    </row>
-    <row r="16" spans="1:20" ht="16.149999999999999" customHeight="1">
-      <c r="A16" s="15"/>
-      <c r="B16" s="16"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="16"/>
-      <c r="H16" s="16"/>
-      <c r="I16" s="16"/>
-      <c r="J16" s="16"/>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="16"/>
-      <c r="O16" s="16"/>
-      <c r="P16" s="16"/>
-      <c r="Q16" s="16"/>
-      <c r="R16" s="17"/>
-    </row>
-    <row r="17" spans="1:20">
+    <row r="16" spans="1:20" s="8" customFormat="1" ht="35.1" customHeight="1">
+      <c r="A16" s="12"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="13"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="13"/>
+      <c r="J16" s="7"/>
+      <c r="K16" s="13"/>
+      <c r="L16" s="7"/>
+      <c r="M16" s="13"/>
+      <c r="N16" s="7"/>
+      <c r="O16" s="13"/>
+      <c r="P16" s="7"/>
+      <c r="Q16" s="13"/>
+      <c r="R16" s="14"/>
+    </row>
+    <row r="17" spans="1:20" ht="16.2" customHeight="1">
       <c r="A17" s="15"/>
       <c r="B17" s="16"/>
       <c r="C17" s="16"/>
@@ -1379,30 +1391,30 @@
       <c r="Q19" s="16"/>
       <c r="R19" s="17"/>
     </row>
-    <row r="20" spans="1:20" ht="19.5">
-      <c r="A20" s="18" t="s">
+    <row r="20" spans="1:20">
+      <c r="A20" s="15"/>
+      <c r="B20" s="16"/>
+      <c r="C20" s="16"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="16"/>
+      <c r="F20" s="16"/>
+      <c r="G20" s="16"/>
+      <c r="H20" s="16"/>
+      <c r="I20" s="16"/>
+      <c r="J20" s="16"/>
+      <c r="K20" s="16"/>
+      <c r="L20" s="16"/>
+      <c r="M20" s="16"/>
+      <c r="N20" s="16"/>
+      <c r="O20" s="16"/>
+      <c r="P20" s="16"/>
+      <c r="Q20" s="16"/>
+      <c r="R20" s="17"/>
+    </row>
+    <row r="21" spans="1:20" ht="19.8">
+      <c r="A21" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="B20" s="19"/>
-      <c r="C20" s="19"/>
-      <c r="D20" s="19"/>
-      <c r="E20" s="19"/>
-      <c r="F20" s="19"/>
-      <c r="G20" s="19"/>
-      <c r="H20" s="19"/>
-      <c r="I20" s="19"/>
-      <c r="J20" s="19"/>
-      <c r="K20" s="19"/>
-      <c r="L20" s="19"/>
-      <c r="M20" s="19"/>
-      <c r="N20" s="19"/>
-      <c r="O20" s="19"/>
-      <c r="P20" s="19"/>
-      <c r="Q20" s="19"/>
-      <c r="R20" s="20"/>
-    </row>
-    <row r="21" spans="1:20" ht="19.5">
-      <c r="A21" s="18"/>
       <c r="B21" s="19"/>
       <c r="C21" s="19"/>
       <c r="D21" s="19"/>
@@ -1421,10 +1433,8 @@
       <c r="Q21" s="19"/>
       <c r="R21" s="20"/>
     </row>
-    <row r="22" spans="1:20" ht="19.5">
-      <c r="A22" s="18" t="s">
-        <v>19</v>
-      </c>
+    <row r="22" spans="1:20" ht="19.8">
+      <c r="A22" s="18"/>
       <c r="B22" s="19"/>
       <c r="C22" s="19"/>
       <c r="D22" s="19"/>
@@ -1443,8 +1453,10 @@
       <c r="Q22" s="19"/>
       <c r="R22" s="20"/>
     </row>
-    <row r="23" spans="1:20" ht="19.5">
-      <c r="A23" s="18"/>
+    <row r="23" spans="1:20" ht="19.8">
+      <c r="A23" s="18" t="s">
+        <v>19</v>
+      </c>
       <c r="B23" s="19"/>
       <c r="C23" s="19"/>
       <c r="D23" s="19"/>
@@ -1463,10 +1475,8 @@
       <c r="Q23" s="19"/>
       <c r="R23" s="20"/>
     </row>
-    <row r="24" spans="1:20" ht="19.5">
-      <c r="A24" s="18" t="s">
-        <v>1</v>
-      </c>
+    <row r="24" spans="1:20" ht="19.8">
+      <c r="A24" s="18"/>
       <c r="B24" s="19"/>
       <c r="C24" s="19"/>
       <c r="D24" s="19"/>
@@ -1485,8 +1495,10 @@
       <c r="Q24" s="19"/>
       <c r="R24" s="20"/>
     </row>
-    <row r="25" spans="1:20" ht="19.5">
-      <c r="A25" s="18"/>
+    <row r="25" spans="1:20" ht="19.8">
+      <c r="A25" s="18" t="s">
+        <v>1</v>
+      </c>
       <c r="B25" s="19"/>
       <c r="C25" s="19"/>
       <c r="D25" s="19"/>
@@ -1504,21 +1516,13 @@
       <c r="P25" s="19"/>
       <c r="Q25" s="19"/>
       <c r="R25" s="20"/>
-      <c r="S25" t="s">
-        <v>0</v>
-      </c>
-      <c r="T25" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:20" ht="19.5">
+    </row>
+    <row r="26" spans="1:20" ht="19.8">
       <c r="A26" s="18"/>
       <c r="B26" s="19"/>
       <c r="C26" s="19"/>
       <c r="D26" s="19"/>
-      <c r="E26" s="19" t="s">
-        <v>26</v>
-      </c>
+      <c r="E26" s="19"/>
       <c r="F26" s="19"/>
       <c r="G26" s="19"/>
       <c r="H26" s="19"/>
@@ -1532,16 +1536,24 @@
       <c r="P26" s="19"/>
       <c r="Q26" s="19"/>
       <c r="R26" s="20"/>
-    </row>
-    <row r="27" spans="1:20" ht="19.5">
+      <c r="S26" t="s">
+        <v>0</v>
+      </c>
+      <c r="T26" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" ht="19.8">
       <c r="A27" s="18"/>
       <c r="B27" s="19"/>
       <c r="C27" s="19"/>
       <c r="D27" s="19"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="21"/>
-      <c r="G27" s="21"/>
-      <c r="H27" s="21"/>
+      <c r="E27" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="F27" s="19"/>
+      <c r="G27" s="19"/>
+      <c r="H27" s="19"/>
       <c r="I27" s="19"/>
       <c r="J27" s="19"/>
       <c r="K27" s="19"/>
@@ -1553,43 +1565,73 @@
       <c r="Q27" s="19"/>
       <c r="R27" s="20"/>
     </row>
-    <row r="28" spans="1:20" ht="19.5">
-      <c r="A28" s="36" t="s">
+    <row r="28" spans="1:20" ht="19.8">
+      <c r="A28" s="18"/>
+      <c r="B28" s="19"/>
+      <c r="C28" s="19"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="21"/>
+      <c r="G28" s="21"/>
+      <c r="H28" s="21"/>
+      <c r="I28" s="19"/>
+      <c r="J28" s="19"/>
+      <c r="K28" s="19"/>
+      <c r="L28" s="19"/>
+      <c r="M28" s="19"/>
+      <c r="N28" s="19"/>
+      <c r="O28" s="19"/>
+      <c r="P28" s="19"/>
+      <c r="Q28" s="19"/>
+      <c r="R28" s="20"/>
+    </row>
+    <row r="29" spans="1:20" ht="19.8">
+      <c r="A29" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="B28" s="37"/>
-      <c r="C28" s="22"/>
-      <c r="D28" s="22"/>
-      <c r="E28" s="28"/>
-      <c r="F28" s="29"/>
-      <c r="G28" s="29"/>
-      <c r="H28" s="22" t="s">
+      <c r="B29" s="46"/>
+      <c r="C29" s="22"/>
+      <c r="D29" s="22"/>
+      <c r="E29" s="39"/>
+      <c r="F29" s="40"/>
+      <c r="G29" s="40"/>
+      <c r="H29" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="I28" s="28"/>
-      <c r="J28" s="29"/>
-      <c r="K28" s="29"/>
-      <c r="L28" s="22" t="s">
+      <c r="I29" s="39"/>
+      <c r="J29" s="40"/>
+      <c r="K29" s="40"/>
+      <c r="L29" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="M28" s="29"/>
-      <c r="N28" s="29"/>
-      <c r="O28" s="29"/>
-      <c r="P28" s="25" t="s">
+      <c r="M29" s="40"/>
+      <c r="N29" s="40"/>
+      <c r="O29" s="40"/>
+      <c r="P29" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="Q28" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="R28" s="24"/>
-    </row>
-    <row r="29" spans="1:20" s="1" customFormat="1" ht="21">
-      <c r="O29" s="6" t="s">
+      <c r="Q29" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="R29" s="24"/>
+    </row>
+    <row r="30" spans="1:20" s="1" customFormat="1" ht="22.2">
+      <c r="O30" s="6" t="s">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="E29:G29"/>
+    <mergeCell ref="I29:K29"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:R5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:R6"/>
+    <mergeCell ref="A8:R8"/>
+    <mergeCell ref="A14:R14"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="M29:O29"/>
     <mergeCell ref="A1:R1"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="C4:R4"/>
@@ -1597,16 +1639,6 @@
     <mergeCell ref="C3:R3"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A3:B3"/>
-    <mergeCell ref="E28:G28"/>
-    <mergeCell ref="I28:K28"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:R5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:R6"/>
-    <mergeCell ref="A8:R8"/>
-    <mergeCell ref="A13:R13"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="M28:O28"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="0.45" bottom="0.41" header="0.48" footer="0.5"/>

--- a/NT_AirPollution.Web/App_Data/Payment/Template/結清證明.xlsx
+++ b/NT_AirPollution.Web/App_Data/Payment/Template/結清證明.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\case\Alvin\NT_AirPollution\NT_AirPollution.Web\App_Data\Payment\Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F60CE23C-AA05-4740-B9A9-6753A6172254}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F85529E8-94DB-4886-B444-594B71CE298F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="14160" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="結清證明" sheetId="60" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="29">
   <si>
     <t xml:space="preserve"> </t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -119,10 +119,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>已依規定向本局申報繳納空氣污染防制費,經結算</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>中  華  民  國</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -134,8 +130,16 @@
     <t>南投縣政府環境保護局</t>
   </si>
   <si>
-    <t xml:space="preserve">該工程已完全結清應繳費額,共計:                     </t>
+    <t xml:space="preserve">                    </t>
     <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">該工程已完全結清應繳費額，共計: </t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>已依規定向本局申報繳納空氣污染防制費，經結算</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -310,7 +314,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -375,15 +379,39 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -408,36 +436,9 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -806,145 +807,145 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:T30"/>
-  <sheetFormatPr defaultRowHeight="16.2"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="15.88671875" customWidth="1"/>
-    <col min="2" max="18" width="4.109375" customWidth="1"/>
+    <col min="1" max="1" width="15.875" customWidth="1"/>
+    <col min="2" max="18" width="4.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="34.35" customHeight="1">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="28"/>
-      <c r="K1" s="28"/>
-      <c r="L1" s="28"/>
-      <c r="M1" s="28"/>
-      <c r="N1" s="28"/>
-      <c r="O1" s="28"/>
-      <c r="P1" s="28"/>
-      <c r="Q1" s="28"/>
-      <c r="R1" s="28"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
+      <c r="K1" s="38"/>
+      <c r="L1" s="38"/>
+      <c r="M1" s="38"/>
+      <c r="N1" s="38"/>
+      <c r="O1" s="38"/>
+      <c r="P1" s="38"/>
+      <c r="Q1" s="38"/>
+      <c r="R1" s="38"/>
       <c r="S1" s="10"/>
     </row>
-    <row r="2" spans="1:20" s="10" customFormat="1" ht="39.9" customHeight="1">
-      <c r="A2" s="37" t="s">
+    <row r="2" spans="1:20" s="10" customFormat="1" ht="39.950000000000003" customHeight="1">
+      <c r="A2" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="33"/>
-      <c r="G2" s="33"/>
-      <c r="H2" s="33"/>
-      <c r="I2" s="33"/>
-      <c r="J2" s="33"/>
-      <c r="K2" s="33"/>
-      <c r="L2" s="33"/>
-      <c r="M2" s="33"/>
-      <c r="N2" s="33"/>
-      <c r="O2" s="33"/>
-      <c r="P2" s="33"/>
-      <c r="Q2" s="33"/>
-      <c r="R2" s="34"/>
+      <c r="B2" s="46"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="41"/>
+      <c r="J2" s="41"/>
+      <c r="K2" s="41"/>
+      <c r="L2" s="41"/>
+      <c r="M2" s="41"/>
+      <c r="N2" s="41"/>
+      <c r="O2" s="41"/>
+      <c r="P2" s="41"/>
+      <c r="Q2" s="41"/>
+      <c r="R2" s="42"/>
       <c r="S2" s="9"/>
     </row>
     <row r="3" spans="1:20" s="9" customFormat="1" ht="34.35" customHeight="1">
-      <c r="A3" s="29" t="s">
+      <c r="A3" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="30"/>
-      <c r="C3" s="35"/>
-      <c r="D3" s="35"/>
-      <c r="E3" s="35"/>
-      <c r="F3" s="35"/>
-      <c r="G3" s="35"/>
-      <c r="H3" s="35"/>
-      <c r="I3" s="35"/>
-      <c r="J3" s="35"/>
-      <c r="K3" s="35"/>
-      <c r="L3" s="35"/>
-      <c r="M3" s="35"/>
-      <c r="N3" s="35"/>
-      <c r="O3" s="35"/>
-      <c r="P3" s="35"/>
-      <c r="Q3" s="35"/>
-      <c r="R3" s="36"/>
+      <c r="B3" s="31"/>
+      <c r="C3" s="43"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="43"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="43"/>
+      <c r="I3" s="43"/>
+      <c r="J3" s="43"/>
+      <c r="K3" s="43"/>
+      <c r="L3" s="43"/>
+      <c r="M3" s="43"/>
+      <c r="N3" s="43"/>
+      <c r="O3" s="43"/>
+      <c r="P3" s="43"/>
+      <c r="Q3" s="43"/>
+      <c r="R3" s="44"/>
     </row>
     <row r="4" spans="1:20" s="9" customFormat="1" ht="68.099999999999994" customHeight="1">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="30"/>
-      <c r="C4" s="31"/>
-      <c r="D4" s="31"/>
-      <c r="E4" s="31"/>
-      <c r="F4" s="31"/>
-      <c r="G4" s="31"/>
-      <c r="H4" s="31"/>
-      <c r="I4" s="31"/>
-      <c r="J4" s="31"/>
-      <c r="K4" s="31"/>
-      <c r="L4" s="31"/>
-      <c r="M4" s="31"/>
-      <c r="N4" s="31"/>
-      <c r="O4" s="31"/>
-      <c r="P4" s="31"/>
-      <c r="Q4" s="31"/>
-      <c r="R4" s="32"/>
+      <c r="B4" s="31"/>
+      <c r="C4" s="39"/>
+      <c r="D4" s="39"/>
+      <c r="E4" s="39"/>
+      <c r="F4" s="39"/>
+      <c r="G4" s="39"/>
+      <c r="H4" s="39"/>
+      <c r="I4" s="39"/>
+      <c r="J4" s="39"/>
+      <c r="K4" s="39"/>
+      <c r="L4" s="39"/>
+      <c r="M4" s="39"/>
+      <c r="N4" s="39"/>
+      <c r="O4" s="39"/>
+      <c r="P4" s="39"/>
+      <c r="Q4" s="39"/>
+      <c r="R4" s="40"/>
     </row>
     <row r="5" spans="1:20" s="9" customFormat="1" ht="34.35" customHeight="1">
-      <c r="A5" s="29" t="s">
+      <c r="A5" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="30"/>
-      <c r="C5" s="30"/>
-      <c r="D5" s="30"/>
-      <c r="E5" s="30"/>
-      <c r="F5" s="30"/>
-      <c r="G5" s="30"/>
-      <c r="H5" s="30"/>
-      <c r="I5" s="30"/>
-      <c r="J5" s="30"/>
-      <c r="K5" s="30"/>
-      <c r="L5" s="30"/>
-      <c r="M5" s="30"/>
-      <c r="N5" s="30"/>
-      <c r="O5" s="30"/>
-      <c r="P5" s="30"/>
-      <c r="Q5" s="30"/>
-      <c r="R5" s="41"/>
+      <c r="B5" s="31"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="31"/>
+      <c r="E5" s="31"/>
+      <c r="F5" s="31"/>
+      <c r="G5" s="31"/>
+      <c r="H5" s="31"/>
+      <c r="I5" s="31"/>
+      <c r="J5" s="31"/>
+      <c r="K5" s="31"/>
+      <c r="L5" s="31"/>
+      <c r="M5" s="31"/>
+      <c r="N5" s="31"/>
+      <c r="O5" s="31"/>
+      <c r="P5" s="31"/>
+      <c r="Q5" s="31"/>
+      <c r="R5" s="32"/>
     </row>
     <row r="6" spans="1:20" s="9" customFormat="1" ht="34.35" customHeight="1">
-      <c r="A6" s="29" t="s">
+      <c r="A6" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="30"/>
-      <c r="C6" s="30"/>
-      <c r="D6" s="30"/>
-      <c r="E6" s="30"/>
-      <c r="F6" s="30"/>
-      <c r="G6" s="30"/>
-      <c r="H6" s="30"/>
-      <c r="I6" s="30"/>
-      <c r="J6" s="30"/>
-      <c r="K6" s="30"/>
-      <c r="L6" s="30"/>
-      <c r="M6" s="30"/>
-      <c r="N6" s="30"/>
-      <c r="O6" s="30"/>
-      <c r="P6" s="30"/>
-      <c r="Q6" s="30"/>
-      <c r="R6" s="41"/>
+      <c r="B6" s="31"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="31"/>
+      <c r="G6" s="31"/>
+      <c r="H6" s="31"/>
+      <c r="I6" s="31"/>
+      <c r="J6" s="31"/>
+      <c r="K6" s="31"/>
+      <c r="L6" s="31"/>
+      <c r="M6" s="31"/>
+      <c r="N6" s="31"/>
+      <c r="O6" s="31"/>
+      <c r="P6" s="31"/>
+      <c r="Q6" s="31"/>
+      <c r="R6" s="32"/>
     </row>
     <row r="7" spans="1:20" ht="35.1" customHeight="1">
       <c r="A7" s="4"/>
@@ -967,26 +968,26 @@
       <c r="R7" s="3"/>
     </row>
     <row r="8" spans="1:20" ht="35.1" customHeight="1">
-      <c r="A8" s="42" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" s="43"/>
-      <c r="C8" s="43"/>
-      <c r="D8" s="43"/>
-      <c r="E8" s="43"/>
-      <c r="F8" s="43"/>
-      <c r="G8" s="43"/>
-      <c r="H8" s="43"/>
-      <c r="I8" s="43"/>
-      <c r="J8" s="43"/>
-      <c r="K8" s="43"/>
-      <c r="L8" s="43"/>
-      <c r="M8" s="43"/>
-      <c r="N8" s="43"/>
-      <c r="O8" s="43"/>
-      <c r="P8" s="43"/>
-      <c r="Q8" s="43"/>
-      <c r="R8" s="44"/>
+      <c r="A8" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="34"/>
+      <c r="C8" s="34"/>
+      <c r="D8" s="34"/>
+      <c r="E8" s="34"/>
+      <c r="F8" s="34"/>
+      <c r="G8" s="34"/>
+      <c r="H8" s="34"/>
+      <c r="I8" s="34"/>
+      <c r="J8" s="34"/>
+      <c r="K8" s="34"/>
+      <c r="L8" s="34"/>
+      <c r="M8" s="34"/>
+      <c r="N8" s="34"/>
+      <c r="O8" s="34"/>
+      <c r="P8" s="34"/>
+      <c r="Q8" s="34"/>
+      <c r="R8" s="35"/>
     </row>
     <row r="9" spans="1:20" s="8" customFormat="1" ht="35.1" customHeight="1">
       <c r="A9" s="27" t="s">
@@ -1101,24 +1102,24 @@
       </c>
     </row>
     <row r="11" spans="1:20" s="8" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A11" s="47"/>
-      <c r="B11" s="50"/>
-      <c r="C11" s="50"/>
-      <c r="D11" s="50"/>
-      <c r="E11" s="50"/>
-      <c r="F11" s="50"/>
-      <c r="G11" s="50"/>
-      <c r="H11" s="50"/>
-      <c r="I11" s="50"/>
-      <c r="J11" s="50"/>
-      <c r="K11" s="50"/>
-      <c r="L11" s="50"/>
-      <c r="M11" s="50"/>
-      <c r="N11" s="50"/>
-      <c r="O11" s="50"/>
-      <c r="P11" s="50"/>
-      <c r="Q11" s="50"/>
-      <c r="R11" s="48"/>
+      <c r="A11" s="18"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="19"/>
+      <c r="K11" s="19"/>
+      <c r="L11" s="19"/>
+      <c r="M11" s="19"/>
+      <c r="N11" s="19"/>
+      <c r="O11" s="19"/>
+      <c r="P11" s="19"/>
+      <c r="Q11" s="19"/>
+      <c r="R11" s="20"/>
     </row>
     <row r="12" spans="1:20" s="8" customFormat="1" ht="35.1" customHeight="1">
       <c r="A12" s="27" t="s">
@@ -1236,26 +1237,28 @@
       </c>
     </row>
     <row r="14" spans="1:20" s="8" customFormat="1" ht="35.1" customHeight="1">
-      <c r="A14" s="42" t="s">
+      <c r="A14" s="47" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" s="48" t="s">
         <v>27</v>
       </c>
-      <c r="B14" s="49"/>
-      <c r="C14" s="49"/>
-      <c r="D14" s="49"/>
-      <c r="E14" s="49"/>
-      <c r="F14" s="49"/>
-      <c r="G14" s="49"/>
-      <c r="H14" s="49"/>
-      <c r="I14" s="49"/>
-      <c r="J14" s="49"/>
-      <c r="K14" s="49"/>
-      <c r="L14" s="49"/>
-      <c r="M14" s="49"/>
-      <c r="N14" s="49"/>
-      <c r="O14" s="49"/>
-      <c r="P14" s="49"/>
-      <c r="Q14" s="49"/>
-      <c r="R14" s="44"/>
+      <c r="C14" s="48"/>
+      <c r="D14" s="48"/>
+      <c r="E14" s="48"/>
+      <c r="F14" s="48"/>
+      <c r="G14" s="48"/>
+      <c r="H14" s="48"/>
+      <c r="I14" s="48"/>
+      <c r="J14" s="48"/>
+      <c r="K14" s="48"/>
+      <c r="L14" s="48"/>
+      <c r="M14" s="48"/>
+      <c r="N14" s="48"/>
+      <c r="O14" s="48"/>
+      <c r="P14" s="48"/>
+      <c r="Q14" s="48"/>
+      <c r="R14" s="49"/>
     </row>
     <row r="15" spans="1:20" s="8" customFormat="1" ht="35.1" customHeight="1">
       <c r="A15" s="26"/>
@@ -1331,7 +1334,7 @@
       <c r="Q16" s="13"/>
       <c r="R16" s="14"/>
     </row>
-    <row r="17" spans="1:20" ht="16.2" customHeight="1">
+    <row r="17" spans="1:20" ht="16.149999999999999" customHeight="1">
       <c r="A17" s="15"/>
       <c r="B17" s="16"/>
       <c r="C17" s="16"/>
@@ -1411,7 +1414,7 @@
       <c r="Q20" s="16"/>
       <c r="R20" s="17"/>
     </row>
-    <row r="21" spans="1:20" ht="19.8">
+    <row r="21" spans="1:20" ht="19.5">
       <c r="A21" s="18" t="s">
         <v>18</v>
       </c>
@@ -1433,7 +1436,7 @@
       <c r="Q21" s="19"/>
       <c r="R21" s="20"/>
     </row>
-    <row r="22" spans="1:20" ht="19.8">
+    <row r="22" spans="1:20" ht="19.5">
       <c r="A22" s="18"/>
       <c r="B22" s="19"/>
       <c r="C22" s="19"/>
@@ -1453,7 +1456,7 @@
       <c r="Q22" s="19"/>
       <c r="R22" s="20"/>
     </row>
-    <row r="23" spans="1:20" ht="19.8">
+    <row r="23" spans="1:20" ht="19.5">
       <c r="A23" s="18" t="s">
         <v>19</v>
       </c>
@@ -1475,7 +1478,7 @@
       <c r="Q23" s="19"/>
       <c r="R23" s="20"/>
     </row>
-    <row r="24" spans="1:20" ht="19.8">
+    <row r="24" spans="1:20" ht="19.5">
       <c r="A24" s="18"/>
       <c r="B24" s="19"/>
       <c r="C24" s="19"/>
@@ -1495,7 +1498,7 @@
       <c r="Q24" s="19"/>
       <c r="R24" s="20"/>
     </row>
-    <row r="25" spans="1:20" ht="19.8">
+    <row r="25" spans="1:20" ht="19.5">
       <c r="A25" s="18" t="s">
         <v>1</v>
       </c>
@@ -1517,7 +1520,7 @@
       <c r="Q25" s="19"/>
       <c r="R25" s="20"/>
     </row>
-    <row r="26" spans="1:20" ht="19.8">
+    <row r="26" spans="1:20" ht="19.5">
       <c r="A26" s="18"/>
       <c r="B26" s="19"/>
       <c r="C26" s="19"/>
@@ -1543,13 +1546,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:20" ht="19.8">
+    <row r="27" spans="1:20" ht="19.5">
       <c r="A27" s="18"/>
       <c r="B27" s="19"/>
       <c r="C27" s="19"/>
       <c r="D27" s="19"/>
       <c r="E27" s="19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F27" s="19"/>
       <c r="G27" s="19"/>
@@ -1565,7 +1568,7 @@
       <c r="Q27" s="19"/>
       <c r="R27" s="20"/>
     </row>
-    <row r="28" spans="1:20" ht="19.8">
+    <row r="28" spans="1:20" ht="19.5">
       <c r="A28" s="18"/>
       <c r="B28" s="19"/>
       <c r="C28" s="19"/>
@@ -1585,43 +1588,50 @@
       <c r="Q28" s="19"/>
       <c r="R28" s="20"/>
     </row>
-    <row r="29" spans="1:20" ht="19.8">
-      <c r="A29" s="45" t="s">
-        <v>24</v>
-      </c>
-      <c r="B29" s="46"/>
+    <row r="29" spans="1:20" ht="19.5">
+      <c r="A29" s="36" t="s">
+        <v>23</v>
+      </c>
+      <c r="B29" s="37"/>
       <c r="C29" s="22"/>
       <c r="D29" s="22"/>
-      <c r="E29" s="39"/>
-      <c r="F29" s="40"/>
-      <c r="G29" s="40"/>
+      <c r="E29" s="28"/>
+      <c r="F29" s="29"/>
+      <c r="G29" s="29"/>
       <c r="H29" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="I29" s="39"/>
-      <c r="J29" s="40"/>
-      <c r="K29" s="40"/>
+      <c r="I29" s="28"/>
+      <c r="J29" s="29"/>
+      <c r="K29" s="29"/>
       <c r="L29" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="M29" s="40"/>
-      <c r="N29" s="40"/>
-      <c r="O29" s="40"/>
+      <c r="M29" s="29"/>
+      <c r="N29" s="29"/>
+      <c r="O29" s="29"/>
       <c r="P29" s="25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q29" s="23" t="s">
         <v>0</v>
       </c>
       <c r="R29" s="24"/>
     </row>
-    <row r="30" spans="1:20" s="1" customFormat="1" ht="22.2">
+    <row r="30" spans="1:20" s="1" customFormat="1" ht="21">
       <c r="O30" s="6" t="s">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="16">
+    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:R4"/>
+    <mergeCell ref="C2:R2"/>
+    <mergeCell ref="C3:R3"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A3:B3"/>
     <mergeCell ref="E29:G29"/>
     <mergeCell ref="I29:K29"/>
     <mergeCell ref="A5:B5"/>
@@ -1629,16 +1639,8 @@
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="C6:R6"/>
     <mergeCell ref="A8:R8"/>
-    <mergeCell ref="A14:R14"/>
     <mergeCell ref="A29:B29"/>
     <mergeCell ref="M29:O29"/>
-    <mergeCell ref="A1:R1"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:R4"/>
-    <mergeCell ref="C2:R2"/>
-    <mergeCell ref="C3:R3"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A3:B3"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="0.45" bottom="0.41" header="0.48" footer="0.5"/>
